--- a/dataset/四省高校汇总表.xlsx
+++ b/dataset/四省高校汇总表.xlsx
@@ -710,7 +710,7 @@
     <t>wyufao@wyu.edu.cn</t>
   </si>
   <si>
-    <t>0750)3296188</t>
+    <t>0750-3296188</t>
   </si>
   <si>
     <t>中山大学深圳校区</t>
@@ -1079,7 +1079,7 @@
     <t>https://zsjyc.neepu.edu.cn/</t>
   </si>
   <si>
-    <t>64806348-</t>
+    <t>64806348</t>
   </si>
   <si>
     <t>http://grad.neepu.edu.cn</t>
@@ -1553,7 +1553,7 @@
     <t>http://www.djtu.edu.cn/Redirect?mid=55</t>
   </si>
   <si>
-    <t>0411-84109958; 0411-86226500-</t>
+    <t>0411-84109958; 0411-86226500</t>
   </si>
   <si>
     <t>http://www.djtu.edu.cn/Redirect?mid=29</t>
@@ -1769,7 +1769,7 @@
     <t>沈农就业</t>
   </si>
   <si>
-    <t>024）88487218</t>
+    <t>024-88487218</t>
   </si>
   <si>
     <t>http://grs.syau.edu.cn/</t>

--- a/dataset/四省高校汇总表.xlsx
+++ b/dataset/四省高校汇总表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6061" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6061" uniqueCount="957">
   <si>
     <t>四省高校汇总表（就业/研究生/国际处 渠道 + 软科排名 + 二维码，按985-211-双一流-双非排列）</t>
   </si>
@@ -623,9 +623,6 @@
     <t>http://yjsc.gdufe.edu.cn</t>
   </si>
   <si>
-    <t>84096846</t>
-  </si>
-  <si>
     <t>http://fao.gdufe.edu.cn/</t>
   </si>
   <si>
@@ -719,6 +716,9 @@
     <t>http://wsc.gzarts.edu.cn/</t>
   </si>
   <si>
+    <t>wsc@gzarts.edu.cn</t>
+  </si>
+  <si>
     <t>广州职业技术大学</t>
   </si>
   <si>
@@ -1866,9 +1866,6 @@
   </si>
   <si>
     <t>http://www.dlufl.edu.cn/info/1121/11447.htm</t>
-  </si>
-  <si>
-    <t>86115896</t>
   </si>
   <si>
     <t>http://ieo.dlufl.edu.cn/</t>
@@ -5330,16 +5327,16 @@
         <v>29</v>
       </c>
       <c r="O29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="P29" s="8" t="s">
+      <c r="Q29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R29" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>29</v>
@@ -5356,7 +5353,7 @@
         <v>21</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>23</v>
@@ -5371,40 +5368,40 @@
         <v>29</v>
       </c>
       <c r="H30" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" s="8" t="s">
+      <c r="Q30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>209</v>
       </c>
       <c r="T30" s="8" t="s">
         <v>29</v>
@@ -5418,7 +5415,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>23</v>
@@ -5433,40 +5430,40 @@
         <v>29</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="M31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P31" s="8" t="s">
+      <c r="Q31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>216</v>
       </c>
       <c r="T31" s="8" t="s">
         <v>29</v>
@@ -5480,7 +5477,7 @@
         <v>21</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>23</v>
@@ -5492,34 +5489,34 @@
         <v>25</v>
       </c>
       <c r="G32" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>221</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>29</v>
@@ -5542,7 +5539,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>23</v>
@@ -5554,31 +5551,31 @@
         <v>25</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="I33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="M33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="M33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N33" s="8" t="s">
+      <c r="O33" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="P33" s="8" t="s">
         <v>29</v>
@@ -5604,7 +5601,7 @@
         <v>21</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>23</v>
@@ -5616,40 +5613,40 @@
         <v>25</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="8" t="s">
+      <c r="M34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="M34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P34" s="8" t="s">
+      <c r="Q34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="S34" s="8" t="s">
         <v>29</v>
@@ -5802,7 +5799,7 @@
         <v>25</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>245</v>
@@ -6422,7 +6419,7 @@
         <v>25</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>329</v>
@@ -6484,7 +6481,7 @@
         <v>25</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>334</v>
@@ -7972,7 +7969,7 @@
         <v>25</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>29</v>
@@ -8282,7 +8279,7 @@
         <v>25</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>507</v>
@@ -9150,7 +9147,7 @@
         <v>25</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>589</v>
@@ -9484,19 +9481,19 @@
         <v>614</v>
       </c>
       <c r="O96" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P96" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="P96" s="8" t="s">
+      <c r="Q96" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R96" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S96" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="Q96" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R96" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S96" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="T96" s="8" t="s">
         <v>29</v>
@@ -9510,7 +9507,7 @@
         <v>561</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>563</v>
@@ -9572,7 +9569,7 @@
         <v>561</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>563</v>
@@ -9584,43 +9581,43 @@
         <v>25</v>
       </c>
       <c r="G98" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="H98" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="H98" s="8" t="s">
+      <c r="I98" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J98" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="I98" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J98" s="8" t="s">
+      <c r="K98" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K98" s="8" t="s">
+      <c r="L98" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L98" s="8" t="s">
+      <c r="M98" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N98" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O98" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P98" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M98" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N98" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O98" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P98" s="8" t="s">
+      <c r="Q98" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R98" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="Q98" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R98" s="8" t="s">
+      <c r="S98" s="8" t="s">
         <v>627</v>
-      </c>
-      <c r="S98" s="8" t="s">
-        <v>628</v>
       </c>
       <c r="T98" s="8" t="s">
         <v>29</v>
@@ -9634,7 +9631,7 @@
         <v>561</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>563</v>
@@ -9646,31 +9643,31 @@
         <v>25</v>
       </c>
       <c r="G99" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="H99" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="H99" s="8" t="s">
+      <c r="I99" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="I99" s="8" t="s">
+      <c r="J99" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L99" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J99" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K99" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L99" s="8" t="s">
+      <c r="M99" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N99" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="M99" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N99" s="8" t="s">
+      <c r="O99" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="O99" s="8" t="s">
-        <v>635</v>
       </c>
       <c r="P99" s="8" t="s">
         <v>29</v>
@@ -9696,7 +9693,7 @@
         <v>561</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>563</v>
@@ -9711,37 +9708,37 @@
         <v>529</v>
       </c>
       <c r="H100" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J100" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="I100" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J100" s="8" t="s">
+      <c r="K100" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="K100" s="8" t="s">
+      <c r="L100" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="L100" s="8" t="s">
+      <c r="M100" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N100" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O100" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="M100" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N100" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O100" s="8" t="s">
+      <c r="P100" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="P100" s="8" t="s">
+      <c r="Q100" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R100" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="Q100" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R100" s="8" t="s">
-        <v>643</v>
       </c>
       <c r="S100" s="8" t="s">
         <v>29</v>
@@ -9758,7 +9755,7 @@
         <v>561</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>563</v>
@@ -9773,19 +9770,19 @@
         <v>442</v>
       </c>
       <c r="H101" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J101" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="I101" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J101" s="8" t="s">
+      <c r="K101" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="K101" s="8" t="s">
+      <c r="L101" s="8" t="s">
         <v>647</v>
-      </c>
-      <c r="L101" s="8" t="s">
-        <v>648</v>
       </c>
       <c r="M101" s="5" t="s">
         <v>29</v>
@@ -9820,7 +9817,7 @@
         <v>561</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>563</v>
@@ -9832,19 +9829,19 @@
         <v>25</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H102" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J102" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K102" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>29</v>
@@ -9882,55 +9879,55 @@
         <v>561</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D103" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="E103" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H103" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="E103" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H103" s="8" t="s">
+      <c r="I103" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="I103" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J103" s="8" t="s">
+      <c r="K103" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="K103" s="8" t="s">
+      <c r="L103" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="L103" s="8" t="s">
+      <c r="M103" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N103" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O103" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="P103" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="M103" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N103" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O103" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="P103" s="8" t="s">
-        <v>658</v>
-      </c>
       <c r="Q103" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R103" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="S103" s="8" t="s">
         <v>655</v>
-      </c>
-      <c r="S103" s="8" t="s">
-        <v>656</v>
       </c>
       <c r="T103" s="8" t="s">
         <v>29</v>
@@ -9944,19 +9941,19 @@
         <v>561</v>
       </c>
       <c r="C104" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="E104" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="H104" s="8" t="s">
         <v>29</v>
@@ -10006,22 +10003,22 @@
         <v>561</v>
       </c>
       <c r="C105" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="D105" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="E105" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="E105" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G105" s="8" t="s">
+      <c r="H105" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>665</v>
       </c>
       <c r="I105" s="5" t="s">
         <v>29</v>
@@ -10068,7 +10065,7 @@
         <v>561</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>575</v>
@@ -10083,31 +10080,31 @@
         <v>29</v>
       </c>
       <c r="H106" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J106" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="I106" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J106" s="8" t="s">
+      <c r="K106" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="K106" s="8" t="s">
+      <c r="L106" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="L106" s="8" t="s">
+      <c r="M106" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N106" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O106" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P106" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="M106" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N106" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O106" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P106" s="8" t="s">
-        <v>671</v>
       </c>
       <c r="Q106" s="5" t="s">
         <v>29</v>
@@ -10130,7 +10127,7 @@
         <v>561</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>575</v>
@@ -10142,7 +10139,7 @@
         <v>25</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>29</v>
@@ -10192,7 +10189,7 @@
         <v>561</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>575</v>
@@ -10204,28 +10201,28 @@
         <v>25</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H108" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J108" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="I108" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J108" s="8" t="s">
+      <c r="K108" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L108" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="K108" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L108" s="8" t="s">
+      <c r="M108" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N108" s="8" t="s">
         <v>677</v>
-      </c>
-      <c r="M108" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N108" s="8" t="s">
-        <v>678</v>
       </c>
       <c r="O108" s="8" t="s">
         <v>29</v>
@@ -10254,7 +10251,7 @@
         <v>561</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>575</v>
@@ -10266,43 +10263,43 @@
         <v>25</v>
       </c>
       <c r="G109" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="H109" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="H109" s="8" t="s">
+      <c r="I109" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="I109" s="8" t="s">
+      <c r="J109" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="J109" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K109" s="8" t="s">
+      <c r="L109" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="L109" s="8" t="s">
+      <c r="M109" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N109" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O109" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="M109" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N109" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O109" s="8" t="s">
+      <c r="P109" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="P109" s="8" t="s">
+      <c r="Q109" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R109" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="Q109" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R109" s="8" t="s">
+      <c r="S109" s="8" t="s">
         <v>687</v>
-      </c>
-      <c r="S109" s="8" t="s">
-        <v>688</v>
       </c>
       <c r="T109" s="8" t="s">
         <v>29</v>
@@ -10316,7 +10313,7 @@
         <v>561</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>575</v>
@@ -10328,34 +10325,34 @@
         <v>25</v>
       </c>
       <c r="G110" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="H110" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="H110" s="8" t="s">
+      <c r="I110" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J110" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="I110" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J110" s="8" t="s">
+      <c r="K110" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L110" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="K110" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L110" s="8" t="s">
+      <c r="M110" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N110" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O110" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="M110" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N110" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O110" s="8" t="s">
+      <c r="P110" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="P110" s="8" t="s">
-        <v>695</v>
       </c>
       <c r="Q110" s="5" t="s">
         <v>29</v>
@@ -10378,7 +10375,7 @@
         <v>561</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>575</v>
@@ -10393,31 +10390,31 @@
         <v>29</v>
       </c>
       <c r="H111" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L111" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="I111" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K111" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L111" s="8" t="s">
+      <c r="M111" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O111" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P111" s="8" t="s">
         <v>698</v>
-      </c>
-      <c r="M111" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N111" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O111" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P111" s="8" t="s">
-        <v>699</v>
       </c>
       <c r="Q111" s="5" t="s">
         <v>29</v>
@@ -10440,7 +10437,7 @@
         <v>561</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>575</v>
@@ -10452,34 +10449,34 @@
         <v>25</v>
       </c>
       <c r="G112" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="H112" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="H112" s="8" t="s">
+      <c r="I112" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J112" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="I112" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J112" s="8" t="s">
+      <c r="K112" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="K112" s="8" t="s">
+      <c r="L112" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="L112" s="8" t="s">
+      <c r="M112" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N112" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O112" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P112" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="M112" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N112" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O112" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P112" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="Q112" s="5" t="s">
         <v>29</v>
@@ -10502,7 +10499,7 @@
         <v>561</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>575</v>
@@ -10514,34 +10511,34 @@
         <v>25</v>
       </c>
       <c r="G113" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H113" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="H113" s="8" t="s">
+      <c r="I113" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J113" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="I113" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J113" s="8" t="s">
+      <c r="K113" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="K113" s="8" t="s">
+      <c r="L113" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="L113" s="8" t="s">
+      <c r="M113" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N113" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O113" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="M113" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N113" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O113" s="8" t="s">
+      <c r="P113" s="8" t="s">
         <v>713</v>
-      </c>
-      <c r="P113" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="Q113" s="5" t="s">
         <v>29</v>
@@ -10564,7 +10561,7 @@
         <v>561</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>575</v>
@@ -10579,31 +10576,31 @@
         <v>29</v>
       </c>
       <c r="H114" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K114" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="I114" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J114" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K114" s="8" t="s">
+      <c r="L114" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="L114" s="8" t="s">
+      <c r="M114" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N114" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O114" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P114" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="M114" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N114" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O114" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P114" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="Q114" s="5" t="s">
         <v>29</v>
@@ -10626,7 +10623,7 @@
         <v>561</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>575</v>
@@ -10641,40 +10638,40 @@
         <v>29</v>
       </c>
       <c r="H115" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J115" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="I115" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J115" s="8" t="s">
+      <c r="K115" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="K115" s="8" t="s">
+      <c r="L115" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="L115" s="8" t="s">
+      <c r="M115" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N115" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O115" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P115" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="M115" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N115" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O115" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P115" s="8" t="s">
-        <v>725</v>
-      </c>
       <c r="Q115" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R115" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="S115" s="8" t="s">
         <v>722</v>
-      </c>
-      <c r="S115" s="8" t="s">
-        <v>723</v>
       </c>
       <c r="T115" s="8" t="s">
         <v>29</v>
@@ -10688,7 +10685,7 @@
         <v>561</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>575</v>
@@ -10703,19 +10700,19 @@
         <v>500</v>
       </c>
       <c r="H116" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L116" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J116" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K116" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L116" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="M116" s="5" t="s">
         <v>29</v>
@@ -10750,7 +10747,7 @@
         <v>561</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>575</v>
@@ -10765,40 +10762,40 @@
         <v>29</v>
       </c>
       <c r="H117" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J117" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="I117" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J117" s="8" t="s">
+      <c r="K117" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="K117" s="8" t="s">
+      <c r="L117" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="L117" s="8" t="s">
+      <c r="M117" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N117" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O117" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P117" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="M117" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N117" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O117" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P117" s="8" t="s">
+      <c r="Q117" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R117" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S117" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="Q117" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R117" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S117" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="T117" s="8" t="s">
         <v>29</v>
@@ -10812,7 +10809,7 @@
         <v>561</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>575</v>
@@ -10827,31 +10824,31 @@
         <v>29</v>
       </c>
       <c r="H118" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L118" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="I118" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K118" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L118" s="8" t="s">
+      <c r="M118" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N118" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O118" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P118" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="M118" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N118" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O118" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P118" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="Q118" s="5" t="s">
         <v>29</v>
@@ -10874,7 +10871,7 @@
         <v>561</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>575</v>
@@ -10889,40 +10886,40 @@
         <v>527</v>
       </c>
       <c r="H119" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K119" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="I119" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J119" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K119" s="8" t="s">
+      <c r="L119" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="L119" s="8" t="s">
+      <c r="M119" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N119" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O119" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P119" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="M119" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N119" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O119" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P119" s="8" t="s">
+      <c r="Q119" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R119" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="Q119" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R119" s="8" t="s">
+      <c r="S119" s="8" t="s">
         <v>745</v>
-      </c>
-      <c r="S119" s="8" t="s">
-        <v>746</v>
       </c>
       <c r="T119" s="8" t="s">
         <v>29</v>
@@ -10936,7 +10933,7 @@
         <v>561</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>575</v>
@@ -10948,7 +10945,7 @@
         <v>25</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H120" s="8" t="s">
         <v>29</v>
@@ -10998,7 +10995,7 @@
         <v>561</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D121" s="8" t="s">
         <v>575</v>
@@ -11010,22 +11007,22 @@
         <v>25</v>
       </c>
       <c r="G121" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="H121" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="I121" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J121" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="I121" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J121" s="8" t="s">
+      <c r="K121" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="K121" s="8" t="s">
+      <c r="L121" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="L121" s="8" t="s">
-        <v>753</v>
       </c>
       <c r="M121" s="5" t="s">
         <v>29</v>
@@ -11060,7 +11057,7 @@
         <v>561</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>575</v>
@@ -11072,22 +11069,22 @@
         <v>25</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H122" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J122" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L122" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="I122" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K122" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L122" s="8" t="s">
-        <v>756</v>
       </c>
       <c r="M122" s="5" t="s">
         <v>29</v>
@@ -11122,46 +11119,46 @@
         <v>561</v>
       </c>
       <c r="C123" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="D123" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="E123" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G123" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="E123" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G123" s="8" t="s">
+      <c r="H123" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="H123" s="8" t="s">
+      <c r="I123" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N123" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O123" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P123" s="8" t="s">
         <v>760</v>
-      </c>
-      <c r="I123" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K123" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L123" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M123" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N123" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O123" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P123" s="8" t="s">
-        <v>761</v>
       </c>
       <c r="Q123" s="5" t="s">
         <v>29</v>
@@ -11184,55 +11181,55 @@
         <v>561</v>
       </c>
       <c r="C124" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="D124" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="E124" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G124" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="E124" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G124" s="8" t="s">
+      <c r="H124" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="H124" s="8" t="s">
+      <c r="I124" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J124" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="I124" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J124" s="8" t="s">
+      <c r="K124" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="K124" s="8" t="s">
+      <c r="L124" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="L124" s="8" t="s">
+      <c r="M124" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N124" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="M124" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N124" s="8" t="s">
+      <c r="O124" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="O124" s="8" t="s">
+      <c r="P124" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="P124" s="8" t="s">
+      <c r="Q124" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R124" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S124" s="8" t="s">
         <v>771</v>
-      </c>
-      <c r="Q124" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R124" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S124" s="8" t="s">
-        <v>772</v>
       </c>
       <c r="T124" s="8" t="s">
         <v>29</v>
@@ -11246,10 +11243,10 @@
         <v>561</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>119</v>
@@ -11261,28 +11258,28 @@
         <v>493</v>
       </c>
       <c r="H125" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J125" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="I125" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J125" s="8" t="s">
+      <c r="K125" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L125" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="K125" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L125" s="8" t="s">
+      <c r="M125" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N125" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O125" s="8" t="s">
         <v>776</v>
-      </c>
-      <c r="M125" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N125" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O125" s="8" t="s">
-        <v>777</v>
       </c>
       <c r="P125" s="8" t="s">
         <v>29</v>
@@ -11308,43 +11305,43 @@
         <v>561</v>
       </c>
       <c r="C126" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G126" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="D126" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G126" s="8" t="s">
+      <c r="H126" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="I126" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J126" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="I126" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J126" s="8" t="s">
+      <c r="K126" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="K126" s="8" t="s">
+      <c r="L126" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="L126" s="8" t="s">
+      <c r="M126" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N126" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O126" s="8" t="s">
         <v>783</v>
-      </c>
-      <c r="M126" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N126" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O126" s="8" t="s">
-        <v>784</v>
       </c>
       <c r="P126" s="8" t="s">
         <v>29</v>
@@ -11370,10 +11367,10 @@
         <v>561</v>
       </c>
       <c r="C127" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="D127" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>786</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>119</v>
@@ -11385,31 +11382,31 @@
         <v>447</v>
       </c>
       <c r="H127" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K127" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L127" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="I127" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K127" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L127" s="8" t="s">
+      <c r="M127" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N127" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O127" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P127" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="M127" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N127" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O127" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P127" s="8" t="s">
-        <v>789</v>
       </c>
       <c r="Q127" s="5" t="s">
         <v>29</v>
@@ -11432,55 +11429,55 @@
         <v>561</v>
       </c>
       <c r="C128" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="D128" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="E128" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H128" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="E128" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H128" s="8" t="s">
+      <c r="I128" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K128" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="I128" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K128" s="8" t="s">
+      <c r="L128" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="L128" s="8" t="s">
+      <c r="M128" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="M128" s="8" t="s">
+      <c r="N128" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="N128" s="8" t="s">
+      <c r="O128" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P128" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="O128" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P128" s="8" t="s">
+      <c r="Q128" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R128" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S128" s="8" t="s">
         <v>797</v>
-      </c>
-      <c r="Q128" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R128" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S128" s="8" t="s">
-        <v>798</v>
       </c>
       <c r="T128" s="8" t="s">
         <v>29</v>
@@ -11494,34 +11491,34 @@
         <v>561</v>
       </c>
       <c r="C129" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G129" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="D129" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G129" s="8" t="s">
+      <c r="H129" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="H129" s="8" t="s">
+      <c r="I129" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L129" s="8" t="s">
         <v>801</v>
-      </c>
-      <c r="I129" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J129" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K129" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L129" s="8" t="s">
-        <v>802</v>
       </c>
       <c r="M129" s="5" t="s">
         <v>29</v>
@@ -11553,13 +11550,13 @@
         <v>128</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="3" t="s">
         <v>804</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>24</v>
@@ -11571,31 +11568,31 @@
         <v>46</v>
       </c>
       <c r="H130" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L130" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="I130" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K130" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L130" s="3" t="s">
+      <c r="M130" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O130" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="M130" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N130" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O130" s="3" t="s">
+      <c r="P130" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="P130" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="Q130" s="5" t="s">
         <v>29</v>
@@ -11615,13 +11612,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>69</v>
@@ -11630,34 +11627,34 @@
         <v>25</v>
       </c>
       <c r="G131" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="H131" s="6" t="s">
         <v>811</v>
       </c>
-      <c r="H131" s="6" t="s">
+      <c r="I131" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J131" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="I131" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J131" s="6" t="s">
+      <c r="K131" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L131" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="K131" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L131" s="6" t="s">
+      <c r="M131" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N131" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O131" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P131" s="6" t="s">
         <v>814</v>
-      </c>
-      <c r="M131" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N131" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O131" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P131" s="6" t="s">
-        <v>815</v>
       </c>
       <c r="Q131" s="5" t="s">
         <v>29</v>
@@ -11677,13 +11674,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>69</v>
@@ -11692,43 +11689,43 @@
         <v>25</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H132" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J132" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="I132" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J132" s="6" t="s">
+      <c r="K132" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="K132" s="6" t="s">
+      <c r="L132" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="L132" s="6" t="s">
+      <c r="M132" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N132" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="M132" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N132" s="6" t="s">
+      <c r="O132" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>821</v>
       </c>
-      <c r="O132" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P132" s="6" t="s">
+      <c r="Q132" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R132" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="Q132" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R132" s="6" t="s">
+      <c r="S132" s="6" t="s">
         <v>823</v>
-      </c>
-      <c r="S132" s="6" t="s">
-        <v>824</v>
       </c>
       <c r="T132" s="6" t="s">
         <v>29</v>
@@ -11739,13 +11736,13 @@
         <v>131</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>69</v>
@@ -11754,43 +11751,43 @@
         <v>25</v>
       </c>
       <c r="G133" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="H133" s="6" t="s">
         <v>826</v>
       </c>
-      <c r="H133" s="6" t="s">
+      <c r="I133" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K133" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="I133" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K133" s="6" t="s">
+      <c r="L133" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="L133" s="6" t="s">
+      <c r="M133" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N133" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O133" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="M133" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N133" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O133" s="6" t="s">
+      <c r="P133" s="6" t="s">
         <v>830</v>
       </c>
-      <c r="P133" s="6" t="s">
+      <c r="Q133" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R133" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S133" s="6" t="s">
         <v>831</v>
-      </c>
-      <c r="Q133" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R133" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S133" s="6" t="s">
-        <v>832</v>
       </c>
       <c r="T133" s="6" t="s">
         <v>29</v>
@@ -11801,49 +11798,49 @@
         <v>132</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C134" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="D134" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="E134" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="H134" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="E134" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>690</v>
-      </c>
-      <c r="H134" s="8" t="s">
+      <c r="I134" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K134" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="I134" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J134" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K134" s="8" t="s">
+      <c r="L134" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="L134" s="8" t="s">
+      <c r="M134" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N134" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O134" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="M134" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N134" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O134" s="8" t="s">
+      <c r="P134" s="8" t="s">
         <v>838</v>
-      </c>
-      <c r="P134" s="8" t="s">
-        <v>839</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>29</v>
@@ -11863,37 +11860,37 @@
         <v>133</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C135" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H135" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="D135" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="H135" s="8" t="s">
+      <c r="I135" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K135" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="I135" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J135" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K135" s="8" t="s">
+      <c r="L135" s="8" t="s">
         <v>842</v>
-      </c>
-      <c r="L135" s="8" t="s">
-        <v>843</v>
       </c>
       <c r="M135" s="5" t="s">
         <v>29</v>
@@ -11925,49 +11922,49 @@
         <v>134</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C136" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G136" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="D136" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G136" s="8" t="s">
+      <c r="H136" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="H136" s="8" t="s">
+      <c r="I136" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L136" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="I136" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J136" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K136" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L136" s="8" t="s">
+      <c r="M136" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N136" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O136" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P136" s="8" t="s">
         <v>847</v>
-      </c>
-      <c r="M136" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N136" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O136" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P136" s="8" t="s">
-        <v>848</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>29</v>
@@ -11987,13 +11984,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E137" s="8" t="s">
         <v>119</v>
@@ -12005,40 +12002,40 @@
         <v>500</v>
       </c>
       <c r="H137" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J137" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K137" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L137" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="I137" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J137" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K137" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L137" s="8" t="s">
+      <c r="M137" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N137" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O137" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P137" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="M137" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N137" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O137" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P137" s="8" t="s">
+      <c r="Q137" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R137" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="Q137" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R137" s="8" t="s">
+      <c r="S137" s="8" t="s">
         <v>853</v>
-      </c>
-      <c r="S137" s="8" t="s">
-        <v>854</v>
       </c>
       <c r="T137" s="8" t="s">
         <v>29</v>
@@ -12049,49 +12046,49 @@
         <v>136</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C138" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="D138" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F138" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H138" s="8" t="s">
+      <c r="I138" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J138" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K138" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="I138" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J138" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K138" s="8" t="s">
+      <c r="L138" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="L138" s="8" t="s">
+      <c r="M138" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N138" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O138" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P138" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="M138" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N138" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O138" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P138" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="Q138" s="5" t="s">
         <v>29</v>
@@ -12111,22 +12108,22 @@
         <v>137</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C139" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G139" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>861</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
@@ -12173,13 +12170,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E140" s="8" t="s">
         <v>119</v>
@@ -12235,49 +12232,49 @@
         <v>139</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C141" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G141" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="D141" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G141" s="8" t="s">
+      <c r="H141" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="H141" s="8" t="s">
+      <c r="I141" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L141" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="I141" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J141" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K141" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L141" s="8" t="s">
+      <c r="M141" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P141" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="M141" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N141" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O141" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P141" s="8" t="s">
-        <v>867</v>
       </c>
       <c r="Q141" s="5" t="s">
         <v>29</v>
@@ -12297,58 +12294,58 @@
         <v>140</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C142" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H142" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="D142" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H142" s="8" t="s">
+      <c r="I142" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K142" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="I142" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J142" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K142" s="8" t="s">
+      <c r="L142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M142" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P142" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="L142" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M142" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N142" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O142" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P142" s="8" t="s">
+      <c r="Q142" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R142" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="Q142" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R142" s="8" t="s">
+      <c r="S142" s="8" t="s">
         <v>872</v>
-      </c>
-      <c r="S142" s="8" t="s">
-        <v>873</v>
       </c>
       <c r="T142" s="8" t="s">
         <v>29</v>
@@ -12359,22 +12356,22 @@
         <v>141</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C143" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G143" s="8" t="s">
         <v>874</v>
-      </c>
-      <c r="D143" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F143" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>875</v>
       </c>
       <c r="H143" s="8" t="s">
         <v>29</v>
@@ -12421,58 +12418,58 @@
         <v>142</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C144" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H144" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="D144" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H144" s="8" t="s">
+      <c r="I144" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J144" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J144" s="8" t="s">
+      <c r="K144" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="K144" s="8" t="s">
+      <c r="L144" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="L144" s="8" t="s">
+      <c r="M144" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N144" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O144" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P144" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="M144" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N144" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O144" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P144" s="8" t="s">
-        <v>881</v>
-      </c>
       <c r="Q144" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R144" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="S144" s="8" t="s">
         <v>878</v>
-      </c>
-      <c r="S144" s="8" t="s">
-        <v>879</v>
       </c>
       <c r="T144" s="8" t="s">
         <v>29</v>
@@ -12483,13 +12480,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E145" s="8" t="s">
         <v>119</v>
@@ -12501,31 +12498,31 @@
         <v>522</v>
       </c>
       <c r="H145" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J145" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K145" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L145" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="I145" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J145" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K145" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L145" s="8" t="s">
+      <c r="M145" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N145" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="M145" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N145" s="8" t="s">
+      <c r="O145" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P145" s="8" t="s">
         <v>885</v>
-      </c>
-      <c r="O145" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P145" s="8" t="s">
-        <v>886</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>29</v>
@@ -12545,37 +12542,37 @@
         <v>144</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C146" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J146" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L146" s="8" t="s">
         <v>887</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F146" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H146" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I146" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J146" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K146" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L146" s="8" t="s">
-        <v>888</v>
       </c>
       <c r="M146" s="8" t="s">
         <v>129</v>
@@ -12607,46 +12604,46 @@
         <v>145</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C147" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G147" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="D147" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G147" s="8" t="s">
+      <c r="H147" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="H147" s="8" t="s">
+      <c r="I147" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J147" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K147" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="I147" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J147" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K147" s="8" t="s">
+      <c r="L147" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="L147" s="8" t="s">
+      <c r="M147" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N147" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O147" s="8" t="s">
         <v>893</v>
-      </c>
-      <c r="M147" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N147" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O147" s="8" t="s">
-        <v>894</v>
       </c>
       <c r="P147" s="8" t="s">
         <v>29</v>
@@ -12669,22 +12666,22 @@
         <v>146</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C148" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G148" s="8" t="s">
         <v>895</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>896</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>29</v>
@@ -12731,13 +12728,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E149" s="8" t="s">
         <v>119</v>
@@ -12749,40 +12746,40 @@
         <v>529</v>
       </c>
       <c r="H149" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J149" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K149" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="I149" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J149" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K149" s="8" t="s">
+      <c r="L149" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="L149" s="8" t="s">
+      <c r="M149" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N149" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O149" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P149" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="M149" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N149" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O149" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P149" s="8" t="s">
+      <c r="Q149" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R149" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S149" s="8" t="s">
         <v>901</v>
-      </c>
-      <c r="Q149" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R149" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S149" s="8" t="s">
-        <v>902</v>
       </c>
       <c r="T149" s="8" t="s">
         <v>29</v>
@@ -12793,13 +12790,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C150" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="D150" s="8" t="s">
         <v>903</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>904</v>
       </c>
       <c r="E150" s="8" t="s">
         <v>119</v>
@@ -12811,37 +12808,37 @@
         <v>469</v>
       </c>
       <c r="H150" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J150" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="I150" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J150" s="8" t="s">
+      <c r="K150" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L150" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="K150" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L150" s="8" t="s">
+      <c r="M150" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N150" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O150" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="M150" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N150" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O150" s="8" t="s">
+      <c r="P150" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="P150" s="8" t="s">
-        <v>909</v>
-      </c>
       <c r="Q150" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R150" s="8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S150" s="8" t="s">
         <v>29</v>
@@ -12855,25 +12852,25 @@
         <v>149</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C151" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G151" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="D151" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="E151" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G151" s="8" t="s">
+      <c r="H151" s="8" t="s">
         <v>911</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>912</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>29</v>
@@ -12917,49 +12914,49 @@
         <v>150</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C152" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="H152" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="D152" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="H152" s="8" t="s">
+      <c r="I152" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L152" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="I152" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J152" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K152" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L152" s="8" t="s">
+      <c r="M152" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P152" s="8" t="s">
         <v>915</v>
-      </c>
-      <c r="M152" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N152" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O152" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P152" s="8" t="s">
-        <v>916</v>
       </c>
       <c r="Q152" s="5" t="s">
         <v>29</v>
@@ -12979,37 +12976,37 @@
         <v>151</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C153" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D153" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="D153" s="8" t="s">
+      <c r="E153" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H153" s="8" t="s">
+      <c r="I153" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J153" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K153" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L153" s="8" t="s">
         <v>919</v>
-      </c>
-      <c r="I153" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J153" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K153" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L153" s="8" t="s">
-        <v>920</v>
       </c>
       <c r="M153" s="5" t="s">
         <v>29</v>
@@ -13041,43 +13038,43 @@
         <v>152</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C154" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="H154" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="D154" s="8" t="s">
-        <v>918</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="H154" s="8" t="s">
+      <c r="I154" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J154" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K154" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L154" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="I154" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J154" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K154" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L154" s="8" t="s">
+      <c r="M154" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N154" s="8" t="s">
         <v>923</v>
-      </c>
-      <c r="M154" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N154" s="8" t="s">
-        <v>924</v>
       </c>
       <c r="O154" s="8" t="s">
         <v>29</v>
@@ -13103,49 +13100,49 @@
         <v>153</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C155" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="D155" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="D155" s="8" t="s">
+      <c r="E155" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G155" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="E155" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G155" s="8" t="s">
+      <c r="H155" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="H155" s="8" t="s">
+      <c r="I155" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J155" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K155" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L155" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M155" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N155" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O155" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P155" s="8" t="s">
         <v>928</v>
-      </c>
-      <c r="I155" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J155" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K155" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L155" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M155" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N155" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O155" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P155" s="8" t="s">
-        <v>929</v>
       </c>
       <c r="Q155" s="5" t="s">
         <v>29</v>
@@ -13165,49 +13162,49 @@
         <v>154</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C156" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="D156" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="D156" s="8" t="s">
+      <c r="E156" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G156" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="E156" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G156" s="8" t="s">
+      <c r="H156" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="H156" s="8" t="s">
+      <c r="I156" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J156" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L156" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M156" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N156" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O156" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P156" s="8" t="s">
         <v>933</v>
-      </c>
-      <c r="I156" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J156" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K156" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L156" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M156" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N156" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O156" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P156" s="8" t="s">
-        <v>934</v>
       </c>
       <c r="Q156" s="5" t="s">
         <v>29</v>
@@ -13227,49 +13224,49 @@
         <v>155</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C157" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="D157" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="D157" s="8" t="s">
+      <c r="E157" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H157" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="E157" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="H157" s="8" t="s">
+      <c r="I157" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J157" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L157" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M157" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N157" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O157" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P157" s="8" t="s">
         <v>937</v>
-      </c>
-      <c r="I157" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J157" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K157" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L157" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M157" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N157" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O157" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P157" s="8" t="s">
-        <v>938</v>
       </c>
       <c r="Q157" s="5" t="s">
         <v>29</v>
@@ -13289,58 +13286,58 @@
         <v>156</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C158" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="D158" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="E158" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H158" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="E158" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H158" s="8" t="s">
+      <c r="I158" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J158" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K158" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="I158" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J158" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K158" s="8" t="s">
+      <c r="L158" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="L158" s="8" t="s">
+      <c r="M158" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N158" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="M158" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N158" s="8" t="s">
+      <c r="O158" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="O158" s="8" t="s">
+      <c r="P158" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="P158" s="8" t="s">
+      <c r="Q158" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R158" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S158" s="8" t="s">
         <v>946</v>
-      </c>
-      <c r="Q158" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R158" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S158" s="8" t="s">
-        <v>947</v>
       </c>
       <c r="T158" s="8" t="s">
         <v>29</v>
@@ -13351,58 +13348,58 @@
         <v>157</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C159" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="H159" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="D159" s="8" t="s">
-        <v>940</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="H159" s="8" t="s">
+      <c r="I159" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J159" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L159" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="I159" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J159" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K159" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L159" s="8" t="s">
+      <c r="M159" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N159" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O159" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P159" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="M159" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N159" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O159" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P159" s="8" t="s">
+      <c r="Q159" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R159" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="Q159" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R159" s="8" t="s">
+      <c r="S159" s="8" t="s">
         <v>952</v>
-      </c>
-      <c r="S159" s="8" t="s">
-        <v>953</v>
       </c>
       <c r="T159" s="8" t="s">
         <v>29</v>
@@ -13796,7 +13793,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15526,16 +15523,16 @@
         <v>29</v>
       </c>
       <c r="O29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="P29" s="8" t="s">
+      <c r="Q29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R29" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>29</v>
@@ -15552,7 +15549,7 @@
         <v>21</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>23</v>
@@ -15567,40 +15564,40 @@
         <v>29</v>
       </c>
       <c r="H30" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" s="8" t="s">
+      <c r="Q30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>209</v>
       </c>
       <c r="T30" s="8" t="s">
         <v>29</v>
@@ -15614,7 +15611,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>23</v>
@@ -15629,40 +15626,40 @@
         <v>29</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="M31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P31" s="8" t="s">
+      <c r="Q31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>216</v>
       </c>
       <c r="T31" s="8" t="s">
         <v>29</v>
@@ -15676,7 +15673,7 @@
         <v>21</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>23</v>
@@ -15688,34 +15685,34 @@
         <v>25</v>
       </c>
       <c r="G32" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>221</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>29</v>
@@ -15738,7 +15735,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>23</v>
@@ -15750,31 +15747,31 @@
         <v>25</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="I33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="M33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="M33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N33" s="8" t="s">
+      <c r="O33" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="P33" s="8" t="s">
         <v>29</v>
@@ -15800,7 +15797,7 @@
         <v>21</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>23</v>
@@ -15812,40 +15809,40 @@
         <v>25</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="8" t="s">
+      <c r="M34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="M34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P34" s="8" t="s">
+      <c r="Q34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="S34" s="8" t="s">
         <v>29</v>
@@ -15998,7 +15995,7 @@
         <v>25</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>245</v>
@@ -16618,7 +16615,7 @@
         <v>25</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>329</v>
@@ -16680,7 +16677,7 @@
         <v>25</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>334</v>
@@ -17575,7 +17572,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18419,7 +18416,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>29</v>
@@ -18729,7 +18726,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>507</v>
@@ -19483,7 +19480,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19769,7 +19766,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>589</v>
@@ -20103,19 +20100,19 @@
         <v>614</v>
       </c>
       <c r="O11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="Q11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S11" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="T11" s="8" t="s">
         <v>29</v>
@@ -20129,7 +20126,7 @@
         <v>561</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>563</v>
@@ -20191,7 +20188,7 @@
         <v>561</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>563</v>
@@ -20203,43 +20200,43 @@
         <v>25</v>
       </c>
       <c r="G13" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="M13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="8" t="s">
+      <c r="Q13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="Q13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="8" t="s">
+      <c r="S13" s="8" t="s">
         <v>627</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>628</v>
       </c>
       <c r="T13" s="8" t="s">
         <v>29</v>
@@ -20253,7 +20250,7 @@
         <v>561</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>563</v>
@@ -20265,31 +20262,31 @@
         <v>25</v>
       </c>
       <c r="G14" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="J14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="8" t="s">
+      <c r="O14" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>635</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>29</v>
@@ -20315,7 +20312,7 @@
         <v>561</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>563</v>
@@ -20330,37 +20327,37 @@
         <v>529</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="M15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="8" t="s">
+      <c r="P15" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="P15" s="8" t="s">
+      <c r="Q15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>643</v>
       </c>
       <c r="S15" s="8" t="s">
         <v>29</v>
@@ -20377,7 +20374,7 @@
         <v>561</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>563</v>
@@ -20392,19 +20389,19 @@
         <v>442</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>647</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>648</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>29</v>
@@ -20439,7 +20436,7 @@
         <v>561</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>563</v>
@@ -20451,19 +20448,19 @@
         <v>25</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>29</v>
@@ -20501,55 +20498,55 @@
         <v>561</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="M18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>658</v>
-      </c>
       <c r="Q18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R18" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="S18" s="8" t="s">
         <v>655</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>656</v>
       </c>
       <c r="T18" s="8" t="s">
         <v>29</v>
@@ -20563,19 +20560,19 @@
         <v>561</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>29</v>
@@ -20625,22 +20622,22 @@
         <v>561</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>665</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>29</v>
@@ -20687,7 +20684,7 @@
         <v>561</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>575</v>
@@ -20702,31 +20699,31 @@
         <v>29</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="M21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>671</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>29</v>
@@ -20749,7 +20746,7 @@
         <v>561</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>575</v>
@@ -20761,7 +20758,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>29</v>
@@ -20811,7 +20808,7 @@
         <v>561</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>575</v>
@@ -20823,28 +20820,28 @@
         <v>25</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="8" t="s">
+      <c r="M23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>677</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>678</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>29</v>
@@ -20873,7 +20870,7 @@
         <v>561</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>575</v>
@@ -20885,43 +20882,43 @@
         <v>25</v>
       </c>
       <c r="G24" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="J24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="M24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="M24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O24" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="P24" s="8" t="s">
+      <c r="Q24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R24" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="Q24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R24" s="8" t="s">
+      <c r="S24" s="8" t="s">
         <v>687</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>688</v>
       </c>
       <c r="T24" s="8" t="s">
         <v>29</v>
@@ -20935,7 +20932,7 @@
         <v>561</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>575</v>
@@ -20947,34 +20944,34 @@
         <v>25</v>
       </c>
       <c r="G25" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="8" t="s">
+      <c r="M25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="8" t="s">
+      <c r="P25" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>695</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>29</v>
@@ -20997,7 +20994,7 @@
         <v>561</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>575</v>
@@ -21012,31 +21009,31 @@
         <v>29</v>
       </c>
       <c r="H26" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L26" s="8" t="s">
+      <c r="M26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>698</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>699</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>29</v>
@@ -21059,7 +21056,7 @@
         <v>561</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>575</v>
@@ -21071,34 +21068,34 @@
         <v>25</v>
       </c>
       <c r="G27" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="L27" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="L27" s="8" t="s">
+      <c r="M27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>29</v>
@@ -21121,7 +21118,7 @@
         <v>561</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>575</v>
@@ -21133,34 +21130,34 @@
         <v>25</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="I28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="K28" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="L28" s="8" t="s">
+      <c r="M28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="M28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="8" t="s">
+      <c r="P28" s="8" t="s">
         <v>713</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>29</v>
@@ -21183,7 +21180,7 @@
         <v>561</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>575</v>
@@ -21198,31 +21195,31 @@
         <v>29</v>
       </c>
       <c r="H29" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="8" t="s">
+      <c r="L29" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="M29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>29</v>
@@ -21245,7 +21242,7 @@
         <v>561</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>575</v>
@@ -21260,40 +21257,40 @@
         <v>29</v>
       </c>
       <c r="H30" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="L30" s="8" t="s">
+      <c r="M30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="M30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>725</v>
-      </c>
       <c r="Q30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R30" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="S30" s="8" t="s">
         <v>722</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>723</v>
       </c>
       <c r="T30" s="8" t="s">
         <v>29</v>
@@ -21307,7 +21304,7 @@
         <v>561</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>575</v>
@@ -21322,19 +21319,19 @@
         <v>500</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>29</v>
@@ -21369,7 +21366,7 @@
         <v>561</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>575</v>
@@ -21384,40 +21381,40 @@
         <v>29</v>
       </c>
       <c r="H32" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="M32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="8" t="s">
+      <c r="Q32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S32" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="T32" s="8" t="s">
         <v>29</v>
@@ -21431,7 +21428,7 @@
         <v>561</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>575</v>
@@ -21446,31 +21443,31 @@
         <v>29</v>
       </c>
       <c r="H33" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="M33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>29</v>
@@ -21493,7 +21490,7 @@
         <v>561</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>575</v>
@@ -21508,40 +21505,40 @@
         <v>527</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="8" t="s">
+      <c r="L34" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="L34" s="8" t="s">
+      <c r="M34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="M34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P34" s="8" t="s">
+      <c r="Q34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="Q34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R34" s="8" t="s">
+      <c r="S34" s="8" t="s">
         <v>745</v>
-      </c>
-      <c r="S34" s="8" t="s">
-        <v>746</v>
       </c>
       <c r="T34" s="8" t="s">
         <v>29</v>
@@ -21555,7 +21552,7 @@
         <v>561</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>575</v>
@@ -21567,7 +21564,7 @@
         <v>25</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>29</v>
@@ -21617,7 +21614,7 @@
         <v>561</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>575</v>
@@ -21629,22 +21626,22 @@
         <v>25</v>
       </c>
       <c r="G36" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="I36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="K36" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="L36" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>753</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>29</v>
@@ -21679,7 +21676,7 @@
         <v>561</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>575</v>
@@ -21691,22 +21688,22 @@
         <v>25</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H37" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>756</v>
       </c>
       <c r="M37" s="5" t="s">
         <v>29</v>
@@ -21741,46 +21738,46 @@
         <v>561</v>
       </c>
       <c r="C38" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="H38" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="I38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>760</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>761</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>29</v>
@@ -21803,55 +21800,55 @@
         <v>561</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="E39" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="8" t="s">
+      <c r="H39" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="I39" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" s="8" t="s">
+      <c r="K39" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="K39" s="8" t="s">
+      <c r="L39" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="M39" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="M39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N39" s="8" t="s">
+      <c r="O39" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="O39" s="8" t="s">
+      <c r="P39" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="P39" s="8" t="s">
+      <c r="Q39" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S39" s="8" t="s">
         <v>771</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S39" s="8" t="s">
-        <v>772</v>
       </c>
       <c r="T39" s="8" t="s">
         <v>29</v>
@@ -21865,10 +21862,10 @@
         <v>561</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>119</v>
@@ -21880,28 +21877,28 @@
         <v>493</v>
       </c>
       <c r="H40" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="8" t="s">
+      <c r="K40" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="K40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L40" s="8" t="s">
+      <c r="M40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>776</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>777</v>
       </c>
       <c r="P40" s="8" t="s">
         <v>29</v>
@@ -21927,43 +21924,43 @@
         <v>561</v>
       </c>
       <c r="C41" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G41" s="8" t="s">
+      <c r="H41" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="I41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="L41" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="L41" s="8" t="s">
+      <c r="M41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O41" s="8" t="s">
         <v>783</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O41" s="8" t="s">
-        <v>784</v>
       </c>
       <c r="P41" s="8" t="s">
         <v>29</v>
@@ -21989,10 +21986,10 @@
         <v>561</v>
       </c>
       <c r="C42" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>786</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>119</v>
@@ -22004,31 +22001,31 @@
         <v>447</v>
       </c>
       <c r="H42" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L42" s="8" t="s">
+      <c r="M42" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>789</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>29</v>
@@ -22051,55 +22048,55 @@
         <v>561</v>
       </c>
       <c r="C43" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="E43" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H43" s="8" t="s">
+      <c r="I43" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K43" s="8" t="s">
+      <c r="L43" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="L43" s="8" t="s">
+      <c r="M43" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="M43" s="8" t="s">
+      <c r="N43" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="N43" s="8" t="s">
+      <c r="O43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P43" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="O43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P43" s="8" t="s">
+      <c r="Q43" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S43" s="8" t="s">
         <v>797</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>798</v>
       </c>
       <c r="T43" s="8" t="s">
         <v>29</v>
@@ -22113,34 +22110,34 @@
         <v>561</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="8" t="s">
+      <c r="H44" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="I44" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>801</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>802</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>29</v>
@@ -22296,7 +22293,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22381,13 +22378,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>804</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>24</v>
@@ -22399,31 +22396,31 @@
         <v>46</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>29</v>
@@ -22443,13 +22440,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>69</v>
@@ -22458,34 +22455,34 @@
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>811</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>814</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>815</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -22505,13 +22502,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>69</v>
@@ -22520,43 +22517,43 @@
         <v>25</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>821</v>
       </c>
-      <c r="O5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6" t="s">
+      <c r="Q5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="Q5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>823</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>824</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>29</v>
@@ -22567,13 +22564,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>69</v>
@@ -22582,43 +22579,43 @@
         <v>25</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>826</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="6" t="s">
+      <c r="L6" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>830</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="Q6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>831</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>832</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>29</v>
@@ -22629,49 +22626,49 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>690</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>838</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>839</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>29</v>
@@ -22691,37 +22688,37 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>842</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>843</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>29</v>
@@ -22753,49 +22750,49 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>847</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>848</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>29</v>
@@ -22815,13 +22812,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>119</v>
@@ -22833,40 +22830,40 @@
         <v>500</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="8" t="s">
+      <c r="M10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" s="8" t="s">
+      <c r="Q10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="Q10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R10" s="8" t="s">
+      <c r="S10" s="8" t="s">
         <v>853</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>854</v>
       </c>
       <c r="T10" s="8" t="s">
         <v>29</v>
@@ -22877,49 +22874,49 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="M11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>29</v>
@@ -22939,22 +22936,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>861</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>29</v>
@@ -23001,13 +22998,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>119</v>
@@ -23063,49 +23060,49 @@
         <v>12</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>867</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>29</v>
@@ -23125,58 +23122,58 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="8" t="s">
+      <c r="Q15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="Q15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="8" t="s">
+      <c r="S15" s="8" t="s">
         <v>872</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>873</v>
       </c>
       <c r="T15" s="8" t="s">
         <v>29</v>
@@ -23187,22 +23184,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>874</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>875</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>29</v>
@@ -23249,58 +23246,58 @@
         <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>881</v>
-      </c>
       <c r="Q17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R17" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="S17" s="8" t="s">
         <v>878</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>879</v>
       </c>
       <c r="T17" s="8" t="s">
         <v>29</v>
@@ -23311,13 +23308,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>119</v>
@@ -23329,31 +23326,31 @@
         <v>522</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="M18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="8" t="s">
+      <c r="O18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>885</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>886</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>29</v>
@@ -23373,37 +23370,37 @@
         <v>17</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>887</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>888</v>
       </c>
       <c r="M19" s="8" t="s">
         <v>129</v>
@@ -23435,46 +23432,46 @@
         <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="M20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>893</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>894</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>29</v>
@@ -23497,22 +23494,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>895</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>896</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>29</v>
@@ -23559,13 +23556,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>119</v>
@@ -23577,40 +23574,40 @@
         <v>529</v>
       </c>
       <c r="H22" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="M22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="M22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P22" s="8" t="s">
+      <c r="Q22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" s="8" t="s">
         <v>901</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>902</v>
       </c>
       <c r="T22" s="8" t="s">
         <v>29</v>
@@ -23621,13 +23618,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>903</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>904</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>119</v>
@@ -23639,37 +23636,37 @@
         <v>469</v>
       </c>
       <c r="H23" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="8" t="s">
+      <c r="M23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="M23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="P23" s="8" t="s">
-        <v>909</v>
-      </c>
       <c r="Q23" s="5" t="s">
         <v>29</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S23" s="8" t="s">
         <v>29</v>
@@ -23683,25 +23680,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>911</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>912</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>29</v>
@@ -23745,49 +23742,49 @@
         <v>23</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="8" t="s">
+      <c r="M25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>915</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>916</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>29</v>
@@ -23807,37 +23804,37 @@
         <v>24</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="I26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>919</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>920</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>29</v>
@@ -23869,43 +23866,43 @@
         <v>25</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>918</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L27" s="8" t="s">
+      <c r="M27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>923</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>924</v>
       </c>
       <c r="O27" s="8" t="s">
         <v>29</v>
@@ -23931,49 +23928,49 @@
         <v>26</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="I28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P28" s="8" t="s">
         <v>928</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>929</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>29</v>
@@ -23993,49 +23990,49 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="I29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>933</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>934</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>29</v>
@@ -24055,49 +24052,49 @@
         <v>28</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="H30" s="8" t="s">
+      <c r="I30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>937</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>938</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>29</v>
@@ -24117,58 +24114,58 @@
         <v>29</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C31" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="8" t="s">
+      <c r="I31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="M31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N31" s="8" t="s">
+      <c r="O31" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="P31" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="P31" s="8" t="s">
+      <c r="Q31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" s="8" t="s">
         <v>946</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>947</v>
       </c>
       <c r="T31" s="8" t="s">
         <v>29</v>
@@ -24179,58 +24176,58 @@
         <v>30</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>940</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" s="8" t="s">
+      <c r="M32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="8" t="s">
+      <c r="Q32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R32" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="Q32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R32" s="8" t="s">
+      <c r="S32" s="8" t="s">
         <v>952</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>953</v>
       </c>
       <c r="T32" s="8" t="s">
         <v>29</v>
